--- a/experiment/ELAN_bestx8/Test/results-Set5/Set5.xlsx
+++ b/experiment/ELAN_bestx8/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.19</v>
+        <v>29.09</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6787</v>
+        <v>0.7786999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.46</v>
+        <v>27.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6774</v>
+        <v>0.7996</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.03</v>
+        <v>22.29</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4774</v>
+        <v>0.7703</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.85</v>
+        <v>30.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6395</v>
+        <v>0.7060999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.8</v>
+        <v>25.36</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6431</v>
+        <v>0.7906</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.47</v>
+        <v>27.01</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6232</v>
+        <v>0.7691</v>
       </c>
     </row>
   </sheetData>
